--- a/REVIEWED_mayor_bronson_20210728_20221120_20260513_autoPush.xlsx
+++ b/REVIEWED_mayor_bronson_20210728_20221120_20260513_autoPush.xlsx
@@ -31283,7 +31283,7 @@
         <v>0</v>
       </c>
       <c r="M604" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N604" t="inlineStr"/>
     </row>

--- a/REVIEWED_mayor_bronson_20210728_20221120_20260513_autoPush.xlsx
+++ b/REVIEWED_mayor_bronson_20210728_20221120_20260513_autoPush.xlsx
@@ -31337,7 +31337,7 @@
         <v>0</v>
       </c>
       <c r="M605" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N605" t="inlineStr"/>
     </row>
